--- a/templates/template.xlsx
+++ b/templates/template.xlsx
@@ -1,163 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1F8A50-9770-41D7-9B51-F8319201B3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="6585" yWindow="1815" windowWidth="26580" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="御請求書" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="会員登録シート" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="補足シート" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
-  <si>
-    <t>御 請 求 書</t>
-  </si>
-  <si>
-    <t>発行日</t>
-  </si>
-  <si>
-    <t>下記の通りご請求申し上げます。何卒よろしくお願い申し上げます。</t>
-  </si>
-  <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>項目</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>単位</t>
-  </si>
-  <si>
-    <t>金額</t>
-  </si>
-  <si>
-    <t>コンサルティング費用</t>
-  </si>
-  <si>
-    <t>式</t>
-  </si>
-  <si>
-    <t>システム保守費用</t>
-  </si>
-  <si>
-    <t>合計金額</t>
-  </si>
-  <si>
-    <t>※本帳票はモックです。振込先口座等の情報はダミーです。</t>
-  </si>
-  <si>
-    <t>${名前}　御中</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>${日付}</t>
-    <rPh sb="2" eb="4">
-      <t>ヒヅケ</t>
-    </rPh>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>${お金①}</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>${お金②}</t>
-    <phoneticPr fontId="6"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>会 員 登 録 シ ー ト</t>
+  </si>
+  <si>
+    <t>氏名</t>
+  </si>
+  <si>
+    <t>${{姓}} ${{名}}</t>
+  </si>
+  <si>
+    <t>住所</t>
+  </si>
+  <si>
+    <t>${{都道府県}}${{住所}}${{番地}} ${{マンションなど}}</t>
+  </si>
+  <si>
+    <t>利用期間</t>
+  </si>
+  <si>
+    <t>${{開始日}} 〜 ${{終了日}}</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>${{サンプルテキスト1}}</t>
+  </si>
+  <si>
+    <t>ポイント残高</t>
+  </si>
+  <si>
+    <t>${{サンプル数値}}</t>
+  </si>
+  <si>
+    <t>メール配信 希望</t>
+  </si>
+  <si>
+    <t>${{チェックボックスtrue}}</t>
+  </si>
+  <si>
+    <t>退会フラグ</t>
+  </si>
+  <si>
+    <t>${{チェックボックスfalse}}</t>
+  </si>
+  <si>
+    <t>発行者住所(補足シート)</t>
+  </si>
+  <si>
+    <t>${{都道府県}}${{住所}}${{番地}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="#,##0&quot;円&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0&quot;pt&quot;"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <sz val="18"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="14"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF888888"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFEFEF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -187,34 +123,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -550,168 +469,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G19"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:D11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B4" s="1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="6" spans="2:7" ht="17.25" x14ac:dyDescent="0.2">
-      <c r="B6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B8" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B11" s="3">
-        <v>1</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="4" t="s">
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C8:D8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B12" s="3">
-        <v>2</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="B1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B13" s="3"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B14" s="3"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B15" s="3"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B16" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="5">
-        <f>SUM(G11:G12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B19" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="C10:D10"/>
-  </mergeCells>
-  <phoneticPr fontId="6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>